--- a/results/graphs_non_dag/benchmark_results.xlsx
+++ b/results/graphs_non_dag/benchmark_results.xlsx
@@ -496,28 +496,28 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.512363076210022</v>
+        <v>0.7825210094451904</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.81914725722128</v>
+        <v>-22.17441012222855</v>
       </c>
       <c r="H2" t="n">
-        <v>-12.81914725722128</v>
+        <v>-17.49677868972492</v>
       </c>
       <c r="I2" t="n">
-        <v>-12.81914725722128</v>
+        <v>-22.17441012222855</v>
       </c>
       <c r="J2" t="n">
-        <v>-12.81914725722128</v>
+        <v>-17.49677868972492</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6.615169811629327</v>
       </c>
       <c r="L2" t="n">
-        <v>42.18945538320843</v>
+        <v>21.09472769160422</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4215134382247925</v>
+        <v>0.516667366027832</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -580,7 +580,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4709049463272095</v>
+        <v>0.5906295776367188</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -589,19 +589,19 @@
         <v>-20.09490929991085</v>
       </c>
       <c r="H4" t="n">
-        <v>-16.45702827856607</v>
+        <v>-20.09490929991085</v>
       </c>
       <c r="I4" t="n">
         <v>-20.09490929991085</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.45702827856607</v>
+        <v>-20.09490929991085</v>
       </c>
       <c r="K4" t="n">
-        <v>5.144740678685482</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>25.78369305946561</v>
+        <v>9.377930735722796</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.386605978012085</v>
+        <v>0.4949400424957275</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -664,28 +664,28 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1460909843444824</v>
+        <v>0.4411255121231079</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
         <v>-12.66100222106747</v>
       </c>
       <c r="H6" t="n">
-        <v>-12.66100222106747</v>
+        <v>-3.440965791678837</v>
       </c>
       <c r="I6" t="n">
         <v>-12.66100222106747</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.66100222106747</v>
+        <v>-3.440965791678837</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13.0391005640154</v>
       </c>
       <c r="L6" t="n">
-        <v>42.9026424997184</v>
+        <v>84.48226684402546</v>
       </c>
     </row>
     <row r="7">
@@ -706,28 +706,28 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2978318929672241</v>
+        <v>0.5690395832061768</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>5.779070637709793</v>
+        <v>15.51205807383335</v>
       </c>
       <c r="H7" t="n">
-        <v>10.64556435577157</v>
+        <v>24.14081977849883</v>
       </c>
       <c r="I7" t="n">
-        <v>5.779070637709793</v>
+        <v>15.51205807383335</v>
       </c>
       <c r="J7" t="n">
-        <v>10.64556435577157</v>
+        <v>24.14081977849883</v>
       </c>
       <c r="K7" t="n">
-        <v>6.882261417286437</v>
+        <v>12.20291182922351</v>
       </c>
       <c r="L7" t="n">
-        <v>84.20893294341766</v>
+        <v>317.7284081107144</v>
       </c>
     </row>
     <row r="8">
@@ -748,28 +748,28 @@
         <v>-677.5780268369093</v>
       </c>
       <c r="E8" t="n">
-        <v>3.919309377670288</v>
+        <v>5.933596014976501</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>-38.72079400709639</v>
+        <v>-28.26229070745384</v>
       </c>
       <c r="H8" t="n">
-        <v>-22.69115260455897</v>
+        <v>-17.46190095473769</v>
       </c>
       <c r="I8" t="n">
-        <v>-38.72079400709639</v>
+        <v>-28.26229070745384</v>
       </c>
       <c r="J8" t="n">
-        <v>-22.69115260455897</v>
+        <v>-17.46190095473769</v>
       </c>
       <c r="K8" t="n">
-        <v>22.66933627144571</v>
+        <v>15.27405766720658</v>
       </c>
       <c r="L8" t="n">
-        <v>96.65113806737705</v>
+        <v>97.42289444711574</v>
       </c>
     </row>
     <row r="9">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-300.3453292967406</v>
+        <v>-300.2639908415947</v>
       </c>
       <c r="E9" t="n">
-        <v>5.738381385803223</v>
+        <v>8.939535975456238</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.30656380987494</v>
+        <v>-47.71586702095202</v>
       </c>
       <c r="H9" t="n">
-        <v>-66.66913268919669</v>
+        <v>-44.03840221518063</v>
       </c>
       <c r="I9" t="n">
-        <v>-72.30656380987494</v>
+        <v>-47.71586702095202</v>
       </c>
       <c r="J9" t="n">
-        <v>-66.66913268919669</v>
+        <v>-44.03840221518063</v>
       </c>
       <c r="K9" t="n">
-        <v>7.972531547807359</v>
+        <v>5.200720603471634</v>
       </c>
       <c r="L9" t="n">
-        <v>77.80250725213452</v>
+        <v>85.33343872112417</v>
       </c>
     </row>
     <row r="10">
@@ -832,28 +832,28 @@
         <v>-677.5780268369093</v>
       </c>
       <c r="E10" t="n">
-        <v>3.967004418373108</v>
+        <v>185.0609805583954</v>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>-30.64274407748977</v>
+        <v>-38.22228321306988</v>
       </c>
       <c r="H10" t="n">
-        <v>-25.23152990272791</v>
+        <v>-22.91924271081201</v>
       </c>
       <c r="I10" t="n">
-        <v>-30.64274407748977</v>
+        <v>-38.22228321306988</v>
       </c>
       <c r="J10" t="n">
-        <v>-25.23152990272791</v>
+        <v>-22.91924271081201</v>
       </c>
       <c r="K10" t="n">
-        <v>7.652612474853757</v>
+        <v>21.64176742383786</v>
       </c>
       <c r="L10" t="n">
-        <v>96.27621780763546</v>
+        <v>96.61747550790507</v>
       </c>
     </row>
     <row r="11">
@@ -871,31 +871,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-300.3453292967406</v>
+        <v>-300.2639908415947</v>
       </c>
       <c r="E11" t="n">
-        <v>3.982303023338318</v>
+        <v>5.815957069396973</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>-35.99769275457271</v>
+        <v>-28.20710964512759</v>
       </c>
       <c r="H11" t="n">
-        <v>-27.90900424126938</v>
+        <v>-17.43431042357457</v>
       </c>
       <c r="I11" t="n">
-        <v>-35.99769275457271</v>
+        <v>-28.20710964512759</v>
       </c>
       <c r="J11" t="n">
-        <v>-27.90900424126938</v>
+        <v>-17.43431042357457</v>
       </c>
       <c r="K11" t="n">
-        <v>11.43913299732503</v>
+        <v>15.23503876384261</v>
       </c>
       <c r="L11" t="n">
-        <v>90.70769493681877</v>
+        <v>94.19367258301308</v>
       </c>
     </row>
     <row r="12">
@@ -916,7 +916,7 @@
         <v>-677.5780268369093</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3423639535903931</v>
+        <v>0.4882645606994629</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -943,31 +943,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-300.3453292967406</v>
+        <v>-300.2639908415947</v>
       </c>
       <c r="E13" t="n">
-        <v>4.061560034751892</v>
+        <v>6.932821989059448</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>27.81865919209086</v>
+        <v>9.885863307230002</v>
       </c>
       <c r="H13" t="n">
-        <v>27.81865919209086</v>
+        <v>9.885863307230002</v>
       </c>
       <c r="I13" t="n">
-        <v>27.81865919209086</v>
+        <v>9.885863307230002</v>
       </c>
       <c r="J13" t="n">
-        <v>27.81865919209086</v>
+        <v>9.885863307230002</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>109.2622246722559</v>
+        <v>103.2923905658888</v>
       </c>
     </row>
     <row r="14">
@@ -988,28 +988,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9872815608978271</v>
+        <v>1.368222117424011</v>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>-26.93998494363935</v>
+        <v>-34.78687850914726</v>
       </c>
       <c r="H14" t="n">
-        <v>-25.72647702766519</v>
+        <v>-29.64992381041915</v>
       </c>
       <c r="I14" t="n">
-        <v>-26.93998494363935</v>
+        <v>-34.78687850914726</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.72647702766519</v>
+        <v>-29.64992381041915</v>
       </c>
       <c r="K14" t="n">
-        <v>1.71615935281776</v>
+        <v>7.264751004237496</v>
       </c>
       <c r="L14" t="n">
-        <v>58.76438332951952</v>
+        <v>52.4756968767769</v>
       </c>
     </row>
     <row r="15">
@@ -1030,7 +1030,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8942190408706665</v>
+        <v>1.237524509429932</v>
       </c>
       <c r="F15" t="n">
         <v>100</v>
@@ -1072,28 +1072,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E16" t="n">
-        <v>1.08682906627655</v>
+        <v>1.585377931594849</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>-35.37356481859351</v>
+        <v>-26.93998494363935</v>
       </c>
       <c r="H16" t="n">
-        <v>-32.41487201378216</v>
+        <v>-24.2920378608862</v>
       </c>
       <c r="I16" t="n">
-        <v>-35.37356481859351</v>
+        <v>-26.93998494363935</v>
       </c>
       <c r="J16" t="n">
-        <v>-32.41487201378216</v>
+        <v>-24.2920378608862</v>
       </c>
       <c r="K16" t="n">
-        <v>4.184223491459908</v>
+        <v>3.744762676875772</v>
       </c>
       <c r="L16" t="n">
-        <v>48.04390685340898</v>
+        <v>61.06357041039401</v>
       </c>
     </row>
     <row r="17">
@@ -1114,7 +1114,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8650374412536621</v>
+        <v>1.468452453613281</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
@@ -1156,7 +1156,7 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02352499961853027</v>
+        <v>0.03983700275421143</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1186,28 +1186,28 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8045890331268311</v>
+        <v>1.346714019775391</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>35.9759881816164</v>
+        <v>3.559469022781407</v>
       </c>
       <c r="H19" t="n">
-        <v>48.02835535103402</v>
+        <v>10.99866083197533</v>
       </c>
       <c r="I19" t="n">
-        <v>35.9759881816164</v>
+        <v>3.559469022781407</v>
       </c>
       <c r="J19" t="n">
-        <v>48.02835535103402</v>
+        <v>10.99866083197533</v>
       </c>
       <c r="K19" t="n">
-        <v>17.04462110969062</v>
+        <v>10.52060594965688</v>
       </c>
       <c r="L19" t="n">
-        <v>321.9005447877575</v>
+        <v>150.8159984391085</v>
       </c>
     </row>
     <row r="20">
@@ -1228,28 +1228,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E20" t="n">
-        <v>1.20660400390625</v>
+        <v>1.607992053031921</v>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>-34.37386734916112</v>
+        <v>-50.54638007892223</v>
       </c>
       <c r="H20" t="n">
-        <v>-33.50022772249098</v>
+        <v>-41.47758989014545</v>
       </c>
       <c r="I20" t="n">
-        <v>-34.37386734916112</v>
+        <v>-50.54638007892223</v>
       </c>
       <c r="J20" t="n">
-        <v>-33.50022772249098</v>
+        <v>-41.47758989014545</v>
       </c>
       <c r="K20" t="n">
-        <v>1.235513008663495</v>
+        <v>12.82520607928419</v>
       </c>
       <c r="L20" t="n">
-        <v>72.80352539124401</v>
+        <v>66.32726709727999</v>
       </c>
     </row>
     <row r="21">
@@ -1270,28 +1270,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9038604497909546</v>
+        <v>1.391797423362732</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.784217390438751</v>
+        <v>-4.989164127734231</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.250730375805926</v>
+        <v>9.046992007344537</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.784217390438751</v>
+        <v>-4.989164127734231</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.250730375805926</v>
+        <v>9.046992007344537</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7544645714436746</v>
+        <v>19.85012236981472</v>
       </c>
       <c r="L21" t="n">
-        <v>77.36512514412804</v>
+        <v>132.7605767001132</v>
       </c>
     </row>
     <row r="22">
@@ -1312,28 +1312,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E22" t="n">
-        <v>1.104263544082642</v>
+        <v>1.855811953544617</v>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>-42.91987067223099</v>
+        <v>-12.17417706384028</v>
       </c>
       <c r="H22" t="n">
-        <v>-28.29542065641672</v>
+        <v>-11.21405768936894</v>
       </c>
       <c r="I22" t="n">
-        <v>-42.91987067223099</v>
+        <v>-12.17417706384028</v>
       </c>
       <c r="J22" t="n">
-        <v>-28.29542065641672</v>
+        <v>-11.21405768936894</v>
       </c>
       <c r="K22" t="n">
-        <v>20.68209555461197</v>
+        <v>1.357813840874534</v>
       </c>
       <c r="L22" t="n">
-        <v>77.02894154030882</v>
+        <v>90.89609665532835</v>
       </c>
     </row>
     <row r="23">
@@ -1354,28 +1354,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8488034009933472</v>
+        <v>1.520504951477051</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>4.591050848238246</v>
+        <v>-15.10149450173126</v>
       </c>
       <c r="H23" t="n">
-        <v>5.431179971211066</v>
+        <v>-10.942855946085</v>
       </c>
       <c r="I23" t="n">
-        <v>4.591050848238246</v>
+        <v>-15.10149450173126</v>
       </c>
       <c r="J23" t="n">
-        <v>5.431179971211066</v>
+        <v>-10.942855946085</v>
       </c>
       <c r="K23" t="n">
-        <v>1.188121999852775</v>
+        <v>5.88120304640259</v>
       </c>
       <c r="L23" t="n">
-        <v>119.667154328702</v>
+        <v>60.37420269090828</v>
       </c>
     </row>
     <row r="24">
@@ -1396,10 +1396,10 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6613818407058716</v>
+        <v>0.4880524873733521</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
         <v>23.0831481424233</v>
@@ -1438,7 +1438,7 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5774574279785156</v>
+        <v>1.075719952583313</v>
       </c>
       <c r="F25" t="n">
         <v>100</v>
@@ -1476,33 +1476,33 @@
           <t>GA</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>-205.8654733793739</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>1.09985339641571</v>
+        <v>1.538751006126404</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.258813272346</v>
+        <v>-7.678103795009773</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.32202407209584</v>
+        <v>-7.531669333427729</v>
       </c>
       <c r="I26" t="n">
-        <v>-23.258813272346</v>
+        <v>-7.678103795009773</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.32202407209584</v>
+        <v>-7.531669333427729</v>
       </c>
       <c r="K26" t="n">
-        <v>11.22431492869008</v>
-      </c>
-      <c r="L26" t="n">
-        <v>92.55726381865887</v>
-      </c>
+        <v>0.2070896015681278</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1522,7 +1522,7 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E27" t="n">
-        <v>1.210066437721252</v>
+        <v>1.715645909309387</v>
       </c>
       <c r="F27" t="n">
         <v>100</v>
@@ -1560,33 +1560,33 @@
           <t>PSO</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>-205.8654733793739</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>1.197944045066833</v>
+        <v>1.996601462364197</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>-21.94429148803959</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="H28" t="n">
-        <v>-14.66476317994264</v>
+        <v>-15.32202407209584</v>
       </c>
       <c r="I28" t="n">
-        <v>-21.94429148803959</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="J28" t="n">
-        <v>-14.66476317994264</v>
+        <v>-15.32202407209584</v>
       </c>
       <c r="K28" t="n">
-        <v>10.29480766098958</v>
-      </c>
-      <c r="L28" t="n">
-        <v>92.8765309989995</v>
-      </c>
+        <v>11.22431492869008</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1606,28 +1606,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E29" t="n">
-        <v>1.193668603897095</v>
+        <v>1.80130410194397</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>-25.87202538446713</v>
+        <v>-29.5157944111409</v>
       </c>
       <c r="H29" t="n">
-        <v>-16.62863012815641</v>
+        <v>-18.45051464149329</v>
       </c>
       <c r="I29" t="n">
-        <v>-25.87202538446713</v>
+        <v>-29.5157944111409</v>
       </c>
       <c r="J29" t="n">
-        <v>-16.62863012815641</v>
+        <v>-18.45051464149329</v>
       </c>
       <c r="K29" t="n">
-        <v>13.07213493384975</v>
+        <v>15.64866872168828</v>
       </c>
       <c r="L29" t="n">
-        <v>75.09472796796531</v>
+        <v>72.36602878673956</v>
       </c>
     </row>
     <row r="30">
@@ -1644,11 +1644,13 @@
           <t>SQA</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>-205.8654733793739</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>0.06610012054443359</v>
+        <v>0.1088529825210571</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1678,7 +1680,7 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9537705183029175</v>
+        <v>1.580966830253601</v>
       </c>
       <c r="F31" t="n">
         <v>100</v>
@@ -1720,7 +1722,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3117254972457886</v>
+        <v>0.4188829660415649</v>
       </c>
       <c r="F32" t="n">
         <v>100</v>
@@ -1762,7 +1764,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E33" t="n">
-        <v>0.249634861946106</v>
+        <v>0.3561880588531494</v>
       </c>
       <c r="F33" t="n">
         <v>100</v>
@@ -1804,7 +1806,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2131525278091431</v>
+        <v>0.3277460336685181</v>
       </c>
       <c r="F34" t="n">
         <v>100</v>
@@ -1846,7 +1848,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1921674013137817</v>
+        <v>0.3002710342407227</v>
       </c>
       <c r="F35" t="n">
         <v>100</v>
@@ -1888,7 +1890,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1466474533081055</v>
+        <v>0.2460285425186157</v>
       </c>
       <c r="F36" t="n">
         <v>100</v>
@@ -1930,7 +1932,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1527199745178223</v>
+        <v>0.2437479496002197</v>
       </c>
       <c r="F37" t="n">
         <v>100</v>
@@ -1969,31 +1971,31 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-306.7022627972041</v>
+        <v>-306.7768162036782</v>
       </c>
       <c r="E38" t="n">
-        <v>2.533966422080994</v>
+        <v>3.816474914550781</v>
       </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>-65.81777317048501</v>
+        <v>-46.65081618882628</v>
       </c>
       <c r="H38" t="n">
-        <v>-64.08700834604582</v>
+        <v>-35.84016011029905</v>
       </c>
       <c r="I38" t="n">
-        <v>-65.81777317048501</v>
+        <v>-46.65081618882628</v>
       </c>
       <c r="J38" t="n">
-        <v>-64.08700834604582</v>
+        <v>-35.84016011029905</v>
       </c>
       <c r="K38" t="n">
-        <v>2.447671088000203</v>
+        <v>15.28857644440435</v>
       </c>
       <c r="L38" t="n">
-        <v>79.10448792860029</v>
+        <v>88.31718753919667</v>
       </c>
     </row>
     <row r="39">
@@ -2014,28 +2016,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E39" t="n">
-        <v>1.687877535820007</v>
+        <v>3.189904570579529</v>
       </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>-24.05623461308152</v>
+        <v>-25.83031925422409</v>
       </c>
       <c r="H39" t="n">
-        <v>-20.00280253724026</v>
+        <v>-21.92694236805011</v>
       </c>
       <c r="I39" t="n">
-        <v>-24.05623461308152</v>
+        <v>-25.83031925422409</v>
       </c>
       <c r="J39" t="n">
-        <v>-20.00280253724026</v>
+        <v>-21.92694236805011</v>
       </c>
       <c r="K39" t="n">
-        <v>5.732418615812837</v>
+        <v>5.520208531480903</v>
       </c>
       <c r="L39" t="n">
-        <v>81.02749907982179</v>
+        <v>79.20246758022934</v>
       </c>
     </row>
     <row r="40">
@@ -2053,31 +2055,31 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-306.7022627972041</v>
+        <v>-306.7768162036782</v>
       </c>
       <c r="E40" t="n">
-        <v>1.956962585449219</v>
+        <v>3.635038137435913</v>
       </c>
       <c r="F40" t="n">
         <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>-47.13446777918767</v>
+        <v>-23.37602711829425</v>
       </c>
       <c r="H40" t="n">
-        <v>-35.90841075818331</v>
+        <v>-21.58056133888049</v>
       </c>
       <c r="I40" t="n">
-        <v>-47.13446777918767</v>
+        <v>-23.37602711829425</v>
       </c>
       <c r="J40" t="n">
-        <v>-35.90841075818331</v>
+        <v>-21.58056133888049</v>
       </c>
       <c r="K40" t="n">
-        <v>15.87604209107807</v>
+        <v>2.53917205602372</v>
       </c>
       <c r="L40" t="n">
-        <v>88.29209460970738</v>
+        <v>92.96538714824118</v>
       </c>
     </row>
     <row r="41">
@@ -2098,28 +2100,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E41" t="n">
-        <v>1.92576003074646</v>
+        <v>2.797154426574707</v>
       </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>-33.72009540661364</v>
+        <v>-31.24807769690011</v>
       </c>
       <c r="H41" t="n">
-        <v>-28.43345990704986</v>
+        <v>-20.27255599636272</v>
       </c>
       <c r="I41" t="n">
-        <v>-33.72009540661364</v>
+        <v>-31.24807769690011</v>
       </c>
       <c r="J41" t="n">
-        <v>-28.43345990704986</v>
+        <v>-20.27255599636272</v>
       </c>
       <c r="K41" t="n">
-        <v>7.476431622806172</v>
+        <v>15.52173164302019</v>
       </c>
       <c r="L41" t="n">
-        <v>73.03108685665299</v>
+        <v>80.77164004497436</v>
       </c>
     </row>
     <row r="42">
@@ -2137,10 +2139,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-306.7022627972041</v>
+        <v>-306.7768162036782</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09497940540313721</v>
+        <v>0.1623749732971191</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2170,28 +2172,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E43" t="n">
-        <v>1.867120027542114</v>
+        <v>3.144873976707458</v>
       </c>
       <c r="F43" t="n">
         <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>14.31172039824721</v>
+        <v>-1.632574181961751</v>
       </c>
       <c r="H43" t="n">
-        <v>14.68928987771931</v>
+        <v>7.26592149347503</v>
       </c>
       <c r="I43" t="n">
-        <v>14.31172039824721</v>
+        <v>-1.632574181961751</v>
       </c>
       <c r="J43" t="n">
-        <v>14.68928987771931</v>
+        <v>7.26592149347503</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5339638786075881</v>
+        <v>12.58437326892103</v>
       </c>
       <c r="L43" t="n">
-        <v>113.9326759439302</v>
+        <v>106.8916694030374</v>
       </c>
     </row>
     <row r="44">
@@ -2212,28 +2214,28 @@
         <v>-358.7245646816248</v>
       </c>
       <c r="E44" t="n">
-        <v>2.162657856941223</v>
+        <v>3.89957594871521</v>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>-32.91316692712152</v>
+        <v>-84.95968083328015</v>
       </c>
       <c r="H44" t="n">
-        <v>-31.02726198612448</v>
+        <v>-48.27323028497427</v>
       </c>
       <c r="I44" t="n">
-        <v>-32.91316692712152</v>
+        <v>-84.95968083328015</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.02726198612448</v>
+        <v>-48.27323028497427</v>
       </c>
       <c r="K44" t="n">
-        <v>2.667072344904436</v>
+        <v>51.88247592074405</v>
       </c>
       <c r="L44" t="n">
-        <v>91.35067262158036</v>
+        <v>86.54309321475721</v>
       </c>
     </row>
     <row r="45">
@@ -2254,28 +2256,28 @@
         <v>-131.6494607579076</v>
       </c>
       <c r="E45" t="n">
-        <v>2.163177490234375</v>
+        <v>2.985529899597168</v>
       </c>
       <c r="F45" t="n">
         <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>-41.32277047352981</v>
+        <v>-11.58677973666839</v>
       </c>
       <c r="H45" t="n">
-        <v>-26.4547751050991</v>
+        <v>-11.58677973666839</v>
       </c>
       <c r="I45" t="n">
-        <v>-41.32277047352981</v>
+        <v>-11.58677973666839</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.4547751050991</v>
+        <v>-11.58677973666839</v>
       </c>
       <c r="K45" t="n">
-        <v>21.02652069533507</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>79.90513979107958</v>
+        <v>91.19876399799654</v>
       </c>
     </row>
     <row r="46">
@@ -2296,28 +2298,28 @@
         <v>-358.7245646816248</v>
       </c>
       <c r="E46" t="n">
-        <v>1.963142991065979</v>
+        <v>3.282665967941284</v>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>-46.00198323115556</v>
+        <v>-35.13211539990285</v>
       </c>
       <c r="H46" t="n">
-        <v>-34.4488006224714</v>
+        <v>-29.01386670684504</v>
       </c>
       <c r="I46" t="n">
-        <v>-46.00198323115556</v>
+        <v>-35.13211539990285</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.4488006224714</v>
+        <v>-29.01386670684504</v>
       </c>
       <c r="K46" t="n">
-        <v>16.33866753377411</v>
+        <v>8.652510279693816</v>
       </c>
       <c r="L46" t="n">
-        <v>90.39686600413177</v>
+        <v>91.91193758013327</v>
       </c>
     </row>
     <row r="47">
@@ -2338,28 +2340,28 @@
         <v>-131.6494607579076</v>
       </c>
       <c r="E47" t="n">
-        <v>2.256253957748413</v>
+        <v>2.982038497924805</v>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>-42.11269745209773</v>
+        <v>-14.25003066270433</v>
       </c>
       <c r="H47" t="n">
-        <v>-26.84973859438306</v>
+        <v>-12.91840519968636</v>
       </c>
       <c r="I47" t="n">
-        <v>-42.11269745209773</v>
+        <v>-14.25003066270433</v>
       </c>
       <c r="J47" t="n">
-        <v>-26.84973859438306</v>
+        <v>-12.91840519968636</v>
       </c>
       <c r="K47" t="n">
-        <v>21.58508341852265</v>
+        <v>1.88320278980137</v>
       </c>
       <c r="L47" t="n">
-        <v>79.60512831590135</v>
+        <v>90.18727070713777</v>
       </c>
     </row>
     <row r="48">
@@ -2380,7 +2382,7 @@
         <v>-358.7245646816248</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1244058609008789</v>
+        <v>0.3238171339035034</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2410,17 +2412,29 @@
         <v>-131.6494607579076</v>
       </c>
       <c r="E49" t="n">
-        <v>1.409353017807007</v>
+        <v>465.2034873962402</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-11.58677973666839</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-11.58677973666839</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-11.58677973666839</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-11.58677973666839</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>91.19876399799654</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2440,28 +2454,28 @@
         <v>-461.3140416175912</v>
       </c>
       <c r="E50" t="n">
-        <v>2.728026032447815</v>
+        <v>5.119904041290283</v>
       </c>
       <c r="F50" t="n">
         <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>-29.51926616207869</v>
+        <v>-49.5442925333759</v>
       </c>
       <c r="H50" t="n">
-        <v>-29.12415182099886</v>
+        <v>-42.20543533715228</v>
       </c>
       <c r="I50" t="n">
-        <v>-29.51926616207869</v>
+        <v>-49.5442925333759</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.12415182099886</v>
+        <v>-42.20543533715228</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5587760598431953</v>
+        <v>10.37871137921882</v>
       </c>
       <c r="L50" t="n">
-        <v>93.68669730518599</v>
+        <v>90.85104039123554</v>
       </c>
     </row>
     <row r="51">
@@ -2482,28 +2496,28 @@
         <v>-170.99101781098</v>
       </c>
       <c r="E51" t="n">
-        <v>2.601621508598328</v>
+        <v>4.630275368690491</v>
       </c>
       <c r="F51" t="n">
         <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>-50.89108117560828</v>
+        <v>-30.7525277583646</v>
       </c>
       <c r="H51" t="n">
-        <v>-45.82485210991059</v>
+        <v>-27.73344940538298</v>
       </c>
       <c r="I51" t="n">
-        <v>-50.89108117560828</v>
+        <v>-30.7525277583646</v>
       </c>
       <c r="J51" t="n">
-        <v>-45.82485210991059</v>
+        <v>-27.73344940538298</v>
       </c>
       <c r="K51" t="n">
-        <v>7.164729854798438</v>
+        <v>4.269621552653625</v>
       </c>
       <c r="L51" t="n">
-        <v>73.20043315926272</v>
+        <v>83.78075657983358</v>
       </c>
     </row>
     <row r="52">
@@ -2524,28 +2538,28 @@
         <v>-461.3140416175912</v>
       </c>
       <c r="E52" t="n">
-        <v>2.478900551795959</v>
+        <v>4.985544443130493</v>
       </c>
       <c r="F52" t="n">
         <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>-40.92639418906549</v>
+        <v>-53.6247963832293</v>
       </c>
       <c r="H52" t="n">
-        <v>-33.91877551108982</v>
+        <v>-42.90377545695834</v>
       </c>
       <c r="I52" t="n">
-        <v>-40.92639418906549</v>
+        <v>-53.6247963832293</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.91877551108982</v>
+        <v>-42.90377545695834</v>
       </c>
       <c r="K52" t="n">
-        <v>9.910269374332215</v>
+        <v>15.16181319641815</v>
       </c>
       <c r="L52" t="n">
-        <v>92.64735680011947</v>
+        <v>90.69965975747955</v>
       </c>
     </row>
     <row r="53">
@@ -2566,28 +2580,28 @@
         <v>-170.99101781098</v>
       </c>
       <c r="E53" t="n">
-        <v>2.486631393432617</v>
+        <v>4.17464816570282</v>
       </c>
       <c r="F53" t="n">
         <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>-50.04934595901817</v>
+        <v>-25.73399456453688</v>
       </c>
       <c r="H53" t="n">
-        <v>-45.48787007404183</v>
+        <v>-14.97451638823957</v>
       </c>
       <c r="I53" t="n">
-        <v>-50.04934595901817</v>
+        <v>-25.73399456453688</v>
       </c>
       <c r="J53" t="n">
-        <v>-45.48787007404183</v>
+        <v>-14.97451638823957</v>
       </c>
       <c r="K53" t="n">
-        <v>6.450901060971355</v>
+        <v>15.21619996097698</v>
       </c>
       <c r="L53" t="n">
-        <v>73.39750902920184</v>
+        <v>91.24251286415934</v>
       </c>
     </row>
     <row r="54">
@@ -2608,7 +2622,7 @@
         <v>-461.3140416175912</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1683554649353027</v>
+        <v>0.2601513862609863</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2638,17 +2652,29 @@
         <v>-170.99101781098</v>
       </c>
       <c r="E55" t="n">
-        <v>2.03557300567627</v>
+        <v>465.9664690494537</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3.161974945077676</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.161974945077676</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3.161974945077676</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.161974945077676</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>101.8492052890012</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2665,31 +2691,31 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-526.1720000078462</v>
+        <v>-526.2075353576067</v>
       </c>
       <c r="E56" t="n">
-        <v>3.013020515441895</v>
+        <v>5.460036396980286</v>
       </c>
       <c r="F56" t="n">
         <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>-43.63521992287426</v>
+        <v>-46.85251984543984</v>
       </c>
       <c r="H56" t="n">
-        <v>-35.25198008057501</v>
+        <v>-44.50440129637308</v>
       </c>
       <c r="I56" t="n">
-        <v>-43.63521992287426</v>
+        <v>-46.85251984543984</v>
       </c>
       <c r="J56" t="n">
-        <v>-35.25198008057501</v>
+        <v>-44.50440129637308</v>
       </c>
       <c r="K56" t="n">
-        <v>11.85569148160608</v>
+        <v>3.320741098150037</v>
       </c>
       <c r="L56" t="n">
-        <v>93.30029342495433</v>
+        <v>91.54242417563857</v>
       </c>
     </row>
     <row r="57">
@@ -2710,28 +2736,28 @@
         <v>-203.7316559616086</v>
       </c>
       <c r="E57" t="n">
-        <v>3.28839099407196</v>
+        <v>5.723078489303589</v>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>-48.8379357662909</v>
+        <v>-46.17168423624149</v>
       </c>
       <c r="H57" t="n">
-        <v>-45.49966382523026</v>
+        <v>-37.61901366037568</v>
       </c>
       <c r="I57" t="n">
-        <v>-48.8379357662909</v>
+        <v>-46.17168423624149</v>
       </c>
       <c r="J57" t="n">
-        <v>-45.49966382523026</v>
+        <v>-37.61901366037568</v>
       </c>
       <c r="K57" t="n">
-        <v>4.721029453937525</v>
+        <v>12.09530272289874</v>
       </c>
       <c r="L57" t="n">
-        <v>77.66686595145318</v>
+        <v>81.5350179711568</v>
       </c>
     </row>
     <row r="58">
@@ -2749,31 +2775,31 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-526.1720000078462</v>
+        <v>-526.2075353576067</v>
       </c>
       <c r="E58" t="n">
-        <v>3.184816002845764</v>
+        <v>5.320870637893677</v>
       </c>
       <c r="F58" t="n">
         <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>-30.86870860961769</v>
+        <v>-60.68673864811034</v>
       </c>
       <c r="H58" t="n">
-        <v>-29.72846976609544</v>
+        <v>-49.13770278980957</v>
       </c>
       <c r="I58" t="n">
-        <v>-30.86870860961769</v>
+        <v>-60.68673864811034</v>
       </c>
       <c r="J58" t="n">
-        <v>-29.72846976609544</v>
+        <v>-49.13770278980957</v>
       </c>
       <c r="K58" t="n">
-        <v>1.612541236853781</v>
+        <v>16.33280314314215</v>
       </c>
       <c r="L58" t="n">
-        <v>94.35004717741496</v>
+        <v>90.66191578643664</v>
       </c>
     </row>
     <row r="59">
@@ -2794,28 +2820,28 @@
         <v>-203.7316559616086</v>
       </c>
       <c r="E59" t="n">
-        <v>2.998876452445984</v>
+        <v>467.5801059007645</v>
       </c>
       <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>-42.78032560079537</v>
+        <v>-68.12780590826047</v>
       </c>
       <c r="H59" t="n">
-        <v>-34.0536384293378</v>
+        <v>-53.20491099988512</v>
       </c>
       <c r="I59" t="n">
-        <v>-42.78032560079537</v>
+        <v>-68.12780590826047</v>
       </c>
       <c r="J59" t="n">
-        <v>-34.0536384293378</v>
+        <v>-53.20491099988512</v>
       </c>
       <c r="K59" t="n">
-        <v>12.3413993524626</v>
+        <v>21.10416036929283</v>
       </c>
       <c r="L59" t="n">
-        <v>83.28505294446981</v>
+        <v>73.88480904022539</v>
       </c>
     </row>
     <row r="60">
@@ -2833,10 +2859,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-526.1720000078462</v>
+        <v>-526.2075353576067</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2497504949569702</v>
+        <v>0.2300959825515747</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2866,7 +2892,7 @@
         <v>-203.7316559616086</v>
       </c>
       <c r="E61" t="n">
-        <v>2.955876469612122</v>
+        <v>4.141227960586548</v>
       </c>
       <c r="F61" t="n">
         <v>100</v>
@@ -2908,28 +2934,28 @@
         <v>-558.4738492635738</v>
       </c>
       <c r="E62" t="n">
-        <v>3.755577445030212</v>
+        <v>5.387650966644287</v>
       </c>
       <c r="F62" t="n">
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>-42.76320975521102</v>
+        <v>-20.46697407643133</v>
       </c>
       <c r="H62" t="n">
-        <v>-32.69350955208976</v>
+        <v>-18.36749589818418</v>
       </c>
       <c r="I62" t="n">
-        <v>-42.76320975521102</v>
+        <v>-20.46697407643133</v>
       </c>
       <c r="J62" t="n">
-        <v>-32.69350955208976</v>
+        <v>-18.36749589818418</v>
       </c>
       <c r="K62" t="n">
-        <v>14.24070659628518</v>
+        <v>2.969110513583483</v>
       </c>
       <c r="L62" t="n">
-        <v>94.1459193487393</v>
+        <v>96.7111269538575</v>
       </c>
     </row>
     <row r="63">
@@ -2947,31 +2973,31 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-212.3084210694507</v>
+        <v>-212.3561226721773</v>
       </c>
       <c r="E63" t="n">
-        <v>4.105573534965515</v>
+        <v>5.438851475715637</v>
       </c>
       <c r="F63" t="n">
         <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>-57.79039500366414</v>
+        <v>-14.11486143824192</v>
       </c>
       <c r="H63" t="n">
-        <v>-47.40913990012331</v>
+        <v>-12.14797399238627</v>
       </c>
       <c r="I63" t="n">
-        <v>-57.79039500366414</v>
+        <v>-14.11486143824192</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.40913990012331</v>
+        <v>-12.14797399238627</v>
       </c>
       <c r="K63" t="n">
-        <v>14.68131176188235</v>
+        <v>2.781598901590433</v>
       </c>
       <c r="L63" t="n">
-        <v>77.66968466850651</v>
+        <v>94.27943313358588</v>
       </c>
     </row>
     <row r="64">
@@ -2992,28 +3018,28 @@
         <v>-558.4738492635738</v>
       </c>
       <c r="E64" t="n">
-        <v>3.471213459968567</v>
+        <v>4.824020504951477</v>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>-17.58070240366242</v>
+        <v>-10.56999156940964</v>
       </c>
       <c r="H64" t="n">
-        <v>-17.23015838031931</v>
+        <v>-5.677777857186769</v>
       </c>
       <c r="I64" t="n">
-        <v>-17.58070240366242</v>
+        <v>-10.56999156940964</v>
       </c>
       <c r="J64" t="n">
-        <v>-17.23015838031931</v>
+        <v>-5.677777857186769</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4957441120206543</v>
+        <v>6.918634981853215</v>
       </c>
       <c r="L64" t="n">
-        <v>96.91477794295299</v>
+        <v>98.98334042593511</v>
       </c>
     </row>
     <row r="65">
@@ -3031,31 +3057,31 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-212.3084210694507</v>
+        <v>-212.3561226721773</v>
       </c>
       <c r="E65" t="n">
-        <v>3.823146104812622</v>
+        <v>468.0003539323807</v>
       </c>
       <c r="F65" t="n">
         <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>-28.14843382940064</v>
+        <v>-42.01192604957268</v>
       </c>
       <c r="H65" t="n">
-        <v>-24.26019199196701</v>
+        <v>-23.44416296167426</v>
       </c>
       <c r="I65" t="n">
-        <v>-28.14843382940064</v>
+        <v>-42.01192604957268</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.26019199196701</v>
+        <v>-23.44416296167426</v>
       </c>
       <c r="K65" t="n">
-        <v>5.498804340285116</v>
+        <v>26.25878238183648</v>
       </c>
       <c r="L65" t="n">
-        <v>88.57313719834458</v>
+        <v>88.95997785857772</v>
       </c>
     </row>
     <row r="66">
@@ -3076,7 +3102,7 @@
         <v>-558.4738492635738</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2933989763259888</v>
+        <v>0.3725000619888306</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3103,20 +3129,32 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-212.3084210694507</v>
+        <v>-212.3561226721773</v>
       </c>
       <c r="E67" t="n">
-        <v>2.697974324226379</v>
+        <v>16.78693449497223</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G67" t="n">
+        <v>35.99374815783182</v>
+      </c>
+      <c r="H67" t="n">
+        <v>35.99374815783182</v>
+      </c>
+      <c r="I67" t="n">
+        <v>35.99374815783182</v>
+      </c>
+      <c r="J67" t="n">
+        <v>35.99374815783182</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>116.9497105639835</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/graphs_non_dag/benchmark_results.xlsx
+++ b/results/graphs_non_dag/benchmark_results.xlsx
@@ -496,7 +496,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2880523204803467</v>
+        <v>0.2592264795303345</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -505,19 +505,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H2" t="n">
-        <v>-16.92044798686654</v>
+        <v>-17.75136782536467</v>
       </c>
       <c r="I2" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.92044798686654</v>
+        <v>-17.75136782536467</v>
       </c>
       <c r="K2" t="n">
-        <v>4.782960072540612</v>
+        <v>4.238958939707864</v>
       </c>
       <c r="L2" t="n">
-        <v>23.69380789117462</v>
+        <v>19.94660634706145</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1396559874216715</v>
+        <v>0.1396709585189819</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -556,7 +556,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8.97195690676443e-16</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1920209725697835</v>
+        <v>0.1817757606506348</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -589,19 +589,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H4" t="n">
-        <v>-18.36282222645356</v>
+        <v>-16.46810807899497</v>
       </c>
       <c r="I4" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J4" t="n">
-        <v>-18.36282222645356</v>
+        <v>-16.46810807899497</v>
       </c>
       <c r="K4" t="n">
-        <v>4.912263230006549</v>
+        <v>3.465455987385825</v>
       </c>
       <c r="L4" t="n">
-        <v>17.18912870631041</v>
+        <v>25.73372645215641</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09760832786560059</v>
+        <v>0.09999216079711915</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -640,7 +640,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.97195690676443e-16</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -664,28 +664,30 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006774584452311198</v>
+        <v>0.006203556060791015</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>-12.66100222106747</v>
+        <v>-12.81914725722128</v>
       </c>
       <c r="H6" t="n">
-        <v>-12.66100222106747</v>
+        <v>-7.939418563553815</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.66100222106747</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-12.66100222106747</v>
+        <v>-12.81914725722128</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="K6" t="n">
-        <v>2.175583928816829e-15</v>
+        <v>9.712200404128902</v>
       </c>
       <c r="L6" t="n">
-        <v>42.90264249971839</v>
+        <v>64.19558166467296</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +708,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07413601875305176</v>
+        <v>0.07283842086791992</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -715,19 +717,19 @@
         <v>5.779070637709793</v>
       </c>
       <c r="H7" t="n">
-        <v>5.779070637709793</v>
+        <v>6.206593831310228</v>
       </c>
       <c r="I7" t="n">
         <v>5.779070637709793</v>
       </c>
       <c r="J7" t="n">
-        <v>5.779070637709793</v>
+        <v>6.206593831310228</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.464520863440212</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.397784529760648</v>
       </c>
     </row>
     <row r="8">
@@ -748,28 +750,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2967589696248372</v>
+        <v>0.3469132614135742</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>-30.33597362503919</v>
+        <v>-48.44913245083486</v>
       </c>
       <c r="H8" t="n">
-        <v>-27.26297589345652</v>
+        <v>-31.62164572302838</v>
       </c>
       <c r="I8" t="n">
-        <v>-30.33597362503919</v>
+        <v>-48.44913245083486</v>
       </c>
       <c r="J8" t="n">
-        <v>-27.26297589345652</v>
+        <v>-31.62164572302838</v>
       </c>
       <c r="K8" t="n">
-        <v>2.924908161954168</v>
+        <v>5.211601061308707</v>
       </c>
       <c r="L8" t="n">
-        <v>56.30161012601146</v>
+        <v>49.31532754670079</v>
       </c>
     </row>
     <row r="9">
@@ -790,7 +792,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1998104254404704</v>
+        <v>0.1970276403427124</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -799,19 +801,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H9" t="n">
-        <v>-21.64409077813305</v>
+        <v>-20.56584922103144</v>
       </c>
       <c r="I9" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J9" t="n">
-        <v>-21.64409077813305</v>
+        <v>-20.56584922103144</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5.397592075596068</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.981690236630114</v>
       </c>
     </row>
     <row r="10">
@@ -832,28 +834,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2707146803538005</v>
+        <v>0.2551342391967774</v>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>-36.78891135342572</v>
+        <v>-40.56679905371724</v>
       </c>
       <c r="H10" t="n">
-        <v>-31.90042325712244</v>
+        <v>-28.76102791145637</v>
       </c>
       <c r="I10" t="n">
-        <v>-36.78891135342572</v>
+        <v>-40.56679905371724</v>
       </c>
       <c r="J10" t="n">
-        <v>-31.90042325712244</v>
+        <v>-28.76102791145637</v>
       </c>
       <c r="K10" t="n">
-        <v>4.233554877496472</v>
+        <v>5.458213085014512</v>
       </c>
       <c r="L10" t="n">
-        <v>48.86848970256525</v>
+        <v>53.90046135230829</v>
       </c>
     </row>
     <row r="11">
@@ -874,7 +876,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1671233177185059</v>
+        <v>0.1566058778762817</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
@@ -883,19 +885,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.204577428808954</v>
+        <v>-20.68144715421032</v>
       </c>
       <c r="I11" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.204577428808954</v>
+        <v>-20.68144715421032</v>
       </c>
       <c r="K11" t="n">
-        <v>14.34183893537354</v>
+        <v>4.769390001619295</v>
       </c>
       <c r="L11" t="n">
-        <v>75.9538181475975</v>
+        <v>4.447604816439272</v>
       </c>
     </row>
     <row r="12">
@@ -916,7 +918,7 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0200812816619873</v>
+        <v>0.01958387851715088</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -954,7 +956,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2317933241526286</v>
+        <v>0.2325899839401245</v>
       </c>
       <c r="F13" t="n">
         <v>100</v>
@@ -963,19 +965,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.31627195818026</v>
+        <v>-8.966278081860844</v>
       </c>
       <c r="I13" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J13" t="n">
-        <v>-11.31627195818026</v>
+        <v>-8.966278081860844</v>
       </c>
       <c r="K13" t="n">
-        <v>17.88830692752427</v>
+        <v>13.99450183655881</v>
       </c>
       <c r="L13" t="n">
-        <v>47.71657504960636</v>
+        <v>58.57401369375403</v>
       </c>
     </row>
     <row r="14">
@@ -996,28 +998,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4990490277608235</v>
+        <v>0.6648346996307373</v>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>-54.5294952383585</v>
+        <v>-75.35989590507279</v>
       </c>
       <c r="H14" t="n">
-        <v>-18.62597482639656</v>
+        <v>-39.08409233567998</v>
       </c>
       <c r="I14" t="n">
-        <v>-54.5294952383585</v>
+        <v>-75.35989590507279</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.62597482639656</v>
+        <v>-39.08409233567998</v>
       </c>
       <c r="K14" t="n">
-        <v>39.13067043796017</v>
+        <v>12.42687070387934</v>
       </c>
       <c r="L14" t="n">
-        <v>84.8788833429531</v>
+        <v>68.27037912640918</v>
       </c>
     </row>
     <row r="15">
@@ -1038,28 +1040,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3923553625742595</v>
+        <v>0.3304558801651001</v>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.334485815726418</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.975474489186964</v>
+        <v>-2.403669056140316</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.334485815726418</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.975474489186964</v>
+        <v>-2.403669056140316</v>
       </c>
       <c r="K15" t="n">
-        <v>4.490805859136585</v>
+        <v>11.39434011463275</v>
       </c>
       <c r="L15" t="n">
-        <v>85.60418348810053</v>
+        <v>91.29593743296709</v>
       </c>
     </row>
     <row r="16">
@@ -1080,28 +1082,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5158839225769043</v>
+        <v>0.4712372589111328</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>-39.51370082630139</v>
+        <v>-71.80719911595767</v>
       </c>
       <c r="H16" t="n">
-        <v>-27.14572154619029</v>
+        <v>-26.02657236477818</v>
       </c>
       <c r="I16" t="n">
-        <v>-39.51370082630139</v>
+        <v>-71.80719911595767</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.14572154619029</v>
+        <v>-26.02657236477818</v>
       </c>
       <c r="K16" t="n">
-        <v>12.60942537415533</v>
+        <v>16.66376248651869</v>
       </c>
       <c r="L16" t="n">
-        <v>77.96230124514422</v>
+        <v>78.87085961518927</v>
       </c>
     </row>
     <row r="17">
@@ -1122,28 +1124,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3041863441467285</v>
+        <v>0.2863969850540161</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.21970440649339</v>
+        <v>-15.10149450173126</v>
       </c>
       <c r="H17" t="n">
-        <v>1.845408858592547</v>
+        <v>-1.391550323478133</v>
       </c>
       <c r="I17" t="n">
-        <v>-10.21970440649339</v>
+        <v>-15.10149450173126</v>
       </c>
       <c r="J17" t="n">
-        <v>1.845408858592547</v>
+        <v>-1.391550323478133</v>
       </c>
       <c r="K17" t="n">
-        <v>10.44895034280819</v>
+        <v>6.464409965323789</v>
       </c>
       <c r="L17" t="n">
-        <v>106.6825148519983</v>
+        <v>94.96097807234013</v>
       </c>
     </row>
     <row r="18">
@@ -1164,10 +1166,10 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03764700889587402</v>
+        <v>0.03673400402069091</v>
       </c>
       <c r="F18" t="n">
-        <v>66.66666666666666</v>
+        <v>88</v>
       </c>
       <c r="G18" t="n">
         <v>23.0831481424233</v>
@@ -1208,28 +1210,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E19" t="n">
-        <v>0.437941312789917</v>
+        <v>0.4431163787841797</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>23.0831481424233</v>
+        <v>7.9510728912868</v>
       </c>
       <c r="H19" t="n">
-        <v>23.0831481424233</v>
+        <v>21.87258212233238</v>
       </c>
       <c r="I19" t="n">
-        <v>23.0831481424233</v>
+        <v>7.9510728912868</v>
       </c>
       <c r="J19" t="n">
-        <v>23.0831481424233</v>
+        <v>21.87258212233238</v>
       </c>
       <c r="K19" t="n">
-        <v>4.351167857633658e-15</v>
+        <v>4.146907628716611</v>
       </c>
       <c r="L19" t="n">
-        <v>183.5876990480395</v>
+        <v>179.2040496627473</v>
       </c>
     </row>
     <row r="20">
@@ -1250,28 +1252,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2596880594889323</v>
+        <v>0.3183314657211304</v>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.385234871845686</v>
+        <v>-54.95794061191005</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.021073990932982</v>
+        <v>-14.94176359816955</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.385234871845686</v>
+        <v>-54.95794061191005</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.021073990932982</v>
+        <v>-14.94176359816955</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6307451478698421</v>
+        <v>13.51407519088717</v>
       </c>
       <c r="L20" t="n">
-        <v>96.58948444550759</v>
+        <v>92.74197690710646</v>
       </c>
     </row>
     <row r="21">
@@ -1292,28 +1294,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1736093362172445</v>
+        <v>0.2331216239929199</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.385234871845686</v>
+        <v>-30.7953932892736</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.385234871845686</v>
+        <v>-10.24319209225417</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.385234871845686</v>
+        <v>-30.7953932892736</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.385234871845686</v>
+        <v>-10.24319209225417</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>6.953064179049838</v>
       </c>
       <c r="L21" t="n">
-        <v>88.93887938535934</v>
+        <v>84.65841842846615</v>
       </c>
     </row>
     <row r="22">
@@ -1334,28 +1336,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7202682495117188</v>
+        <v>0.3435420227050781</v>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>-38.96379066863481</v>
+        <v>-50.28897681984679</v>
       </c>
       <c r="H22" t="n">
-        <v>-26.02902293980196</v>
+        <v>-14.78101032120997</v>
       </c>
       <c r="I22" t="n">
-        <v>-38.96379066863481</v>
+        <v>-50.28897681984679</v>
       </c>
       <c r="J22" t="n">
-        <v>-26.02902293980196</v>
+        <v>-14.78101032120997</v>
       </c>
       <c r="K22" t="n">
-        <v>11.27140847887246</v>
+        <v>10.93980281345485</v>
       </c>
       <c r="L22" t="n">
-        <v>87.35629510256193</v>
+        <v>92.82006347224085</v>
       </c>
     </row>
     <row r="23">
@@ -1376,28 +1378,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2970132033030192</v>
+        <v>0.2698701620101929</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>-15.81744936192374</v>
+        <v>-37.45491248806763</v>
       </c>
       <c r="H23" t="n">
-        <v>-10.19597303520504</v>
+        <v>-10.79751035980553</v>
       </c>
       <c r="I23" t="n">
-        <v>-15.81744936192374</v>
+        <v>-37.45491248806763</v>
       </c>
       <c r="J23" t="n">
-        <v>-10.19597303520504</v>
+        <v>-10.79751035980553</v>
       </c>
       <c r="K23" t="n">
-        <v>4.868341305711228</v>
+        <v>6.319494424678306</v>
       </c>
       <c r="L23" t="n">
-        <v>84.72914003643035</v>
+        <v>83.82819686846426</v>
       </c>
     </row>
     <row r="24">
@@ -1418,25 +1420,31 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06314468383789062</v>
+        <v>0.06154125690460205</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>4.864753555590494e-16</v>
+      </c>
+      <c r="L24" t="n">
+        <v>101.5553545207369</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1456,28 +1464,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7400313218434652</v>
+        <v>0.7373441219329834</v>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>3.201937946842596</v>
+        <v>-17.19124270677605</v>
       </c>
       <c r="H25" t="n">
-        <v>3.201937946842596</v>
+        <v>-1.017307880957558</v>
       </c>
       <c r="I25" t="n">
-        <v>3.201937946842596</v>
+        <v>-17.19124270677605</v>
       </c>
       <c r="J25" t="n">
-        <v>3.201937946842596</v>
+        <v>-1.017307880957558</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>5.612246373834981</v>
       </c>
       <c r="L25" t="n">
-        <v>104.7956527375506</v>
+        <v>98.47634295066314</v>
       </c>
     </row>
     <row r="26">
@@ -1498,7 +1506,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1012174288431803</v>
+        <v>0.1014697551727295</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
@@ -1516,7 +1524,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1540,7 +1548,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07268102963765462</v>
+        <v>0.07296319961547852</v>
       </c>
       <c r="F27" t="n">
         <v>100</v>
@@ -1558,7 +1566,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1582,7 +1590,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0583336353302002</v>
+        <v>0.06036032199859619</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -1600,7 +1608,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1624,7 +1632,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03819998105367025</v>
+        <v>0.04112500190734864</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
@@ -1642,7 +1650,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1666,7 +1674,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00333102544148763</v>
+        <v>0.002999005317687988</v>
       </c>
       <c r="F30" t="n">
         <v>100</v>
@@ -1684,7 +1692,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1708,7 +1716,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03406238555908203</v>
+        <v>0.03423496246337891</v>
       </c>
       <c r="F31" t="n">
         <v>100</v>
@@ -1726,7 +1734,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1750,28 +1758,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9278706709543864</v>
+        <v>0.858689637184143</v>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>-98.79840701612258</v>
+        <v>-83.17558374340292</v>
       </c>
       <c r="H32" t="n">
-        <v>-57.36367239943493</v>
+        <v>-40.87957988141083</v>
       </c>
       <c r="I32" t="n">
-        <v>-98.79840701612258</v>
+        <v>-83.17558374340292</v>
       </c>
       <c r="J32" t="n">
-        <v>-57.36367239943493</v>
+        <v>-40.87957988141083</v>
       </c>
       <c r="K32" t="n">
-        <v>36.99399303158665</v>
+        <v>15.72166587720408</v>
       </c>
       <c r="L32" t="n">
-        <v>81.29662563416932</v>
+        <v>86.67124933850226</v>
       </c>
     </row>
     <row r="33">
@@ -1792,28 +1800,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7161103089650472</v>
+        <v>0.7015517997741699</v>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>-47.68016226790908</v>
+        <v>-73.82012908285937</v>
       </c>
       <c r="H33" t="n">
-        <v>-44.93711506412806</v>
+        <v>-33.40258291847693</v>
       </c>
       <c r="I33" t="n">
-        <v>-47.68016226790908</v>
+        <v>-73.82012908285937</v>
       </c>
       <c r="J33" t="n">
-        <v>-44.93711506412806</v>
+        <v>-33.40258291847693</v>
       </c>
       <c r="K33" t="n">
-        <v>2.445400009955319</v>
+        <v>14.52523431881931</v>
       </c>
       <c r="L33" t="n">
-        <v>57.37749971200034</v>
+        <v>68.31791275361125</v>
       </c>
     </row>
     <row r="34">
@@ -1834,28 +1842,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E34" t="n">
-        <v>1.034568707148234</v>
+        <v>0.6787927627563477</v>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>-64.86209432582574</v>
+        <v>-67.34428852594259</v>
       </c>
       <c r="H34" t="n">
-        <v>-40.440549068253</v>
+        <v>-29.93657616265235</v>
       </c>
       <c r="I34" t="n">
-        <v>-64.86209432582574</v>
+        <v>-67.34428852594259</v>
       </c>
       <c r="J34" t="n">
-        <v>-40.440549068253</v>
+        <v>-29.93657616265235</v>
       </c>
       <c r="K34" t="n">
-        <v>23.14230882694738</v>
+        <v>12.96543610986399</v>
       </c>
       <c r="L34" t="n">
-        <v>86.81439494465259</v>
+        <v>90.23920596815198</v>
       </c>
     </row>
     <row r="35">
@@ -1876,28 +1884,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5404263337453207</v>
+        <v>0.5811501741409302</v>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>-37.27915660494482</v>
+        <v>-48.70961047200002</v>
       </c>
       <c r="H35" t="n">
-        <v>-28.99571254776091</v>
+        <v>-26.55325452426786</v>
       </c>
       <c r="I35" t="n">
-        <v>-37.27915660494482</v>
+        <v>-48.70961047200002</v>
       </c>
       <c r="J35" t="n">
-        <v>-28.99571254776091</v>
+        <v>-26.55325452426786</v>
       </c>
       <c r="K35" t="n">
-        <v>7.175725975210004</v>
+        <v>10.15771262887356</v>
       </c>
       <c r="L35" t="n">
-        <v>72.49779464805358</v>
+        <v>74.81444687775718</v>
       </c>
     </row>
     <row r="36">
@@ -1918,7 +1926,7 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09455029169718425</v>
+        <v>0.09215949535369873</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1956,19 +1964,19 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E37" t="n">
-        <v>1.130656003952026</v>
+        <v>1.089952220916748</v>
       </c>
       <c r="F37" t="n">
-        <v>33.33333333333333</v>
+        <v>66</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.632574181961751</v>
+        <v>-7.544969236804366</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.632574181961751</v>
+        <v>12.52536774204873</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.632574181961751</v>
+        <v>-7.544969236804366</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1976,10 +1984,10 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>16.72522542298737</v>
       </c>
       <c r="L37" t="n">
-        <v>98.45151622569574</v>
+        <v>111.8802128136379</v>
       </c>
     </row>
   </sheetData>

--- a/results/graphs_non_dag/benchmark_results.xlsx
+++ b/results/graphs_non_dag/benchmark_results.xlsx
@@ -496,7 +496,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2592264795303345</v>
+        <v>0.5500526428222656</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -505,19 +505,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H2" t="n">
-        <v>-17.75136782536467</v>
+        <v>-15.9375682122237</v>
       </c>
       <c r="I2" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J2" t="n">
-        <v>-17.75136782536467</v>
+        <v>-15.9375682122237</v>
       </c>
       <c r="K2" t="n">
-        <v>4.238958939707864</v>
+        <v>5.401263533451655</v>
       </c>
       <c r="L2" t="n">
-        <v>19.94660634706145</v>
+        <v>28.12630358880562</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1396709585189819</v>
+        <v>0.4201946258544922</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -556,7 +556,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K3" t="n">
-        <v>8.97195690676443e-16</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1817757606506348</v>
+        <v>0.506061315536499</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -589,19 +589,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H4" t="n">
-        <v>-16.46810807899497</v>
+        <v>-19.3457020010964</v>
       </c>
       <c r="I4" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.46810807899497</v>
+        <v>-19.3457020010964</v>
       </c>
       <c r="K4" t="n">
-        <v>3.465455987385825</v>
+        <v>3.268361972261306</v>
       </c>
       <c r="L4" t="n">
-        <v>25.73372645215641</v>
+        <v>12.75663300867941</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09999216079711915</v>
+        <v>0.3809603055318196</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -640,7 +640,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K5" t="n">
-        <v>8.97195690676443e-16</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -664,19 +664,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006203556060791015</v>
+        <v>0.6743262608846029</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>-12.81914725722128</v>
+        <v>18.48045501250461</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.939418563553815</v>
+        <v>18.48045501250461</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.81914725722128</v>
+        <v>18.48045501250461</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9.712200404128902</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>64.19558166467296</v>
+        <v>183.3413602014109</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +708,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07283842086791992</v>
+        <v>7.364137411117554</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -717,19 +717,19 @@
         <v>5.779070637709793</v>
       </c>
       <c r="H7" t="n">
-        <v>6.206593831310228</v>
+        <v>5.779070637709793</v>
       </c>
       <c r="I7" t="n">
         <v>5.779070637709793</v>
       </c>
       <c r="J7" t="n">
-        <v>6.206593831310228</v>
+        <v>5.779070637709793</v>
       </c>
       <c r="K7" t="n">
-        <v>1.464520863440212</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7.397784529760648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -750,28 +750,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3469132614135742</v>
+        <v>1.04619296391805</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>-48.44913245083486</v>
+        <v>-37.51101427360693</v>
       </c>
       <c r="H8" t="n">
-        <v>-31.62164572302838</v>
+        <v>-32.22203977511564</v>
       </c>
       <c r="I8" t="n">
-        <v>-48.44913245083486</v>
+        <v>-37.51101427360693</v>
       </c>
       <c r="J8" t="n">
-        <v>-31.62164572302838</v>
+        <v>-32.22203977511564</v>
       </c>
       <c r="K8" t="n">
-        <v>5.211601061308707</v>
+        <v>9.160772551323042</v>
       </c>
       <c r="L8" t="n">
-        <v>49.31532754670079</v>
+        <v>48.35298750470891</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1970276403427124</v>
+        <v>0.9062723318735758</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -801,19 +801,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.56584922103144</v>
+        <v>-21.64409077813305</v>
       </c>
       <c r="I9" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J9" t="n">
-        <v>-20.56584922103144</v>
+        <v>-21.64409077813305</v>
       </c>
       <c r="K9" t="n">
-        <v>5.397592075596068</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4.981690236630114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -834,28 +834,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2551342391967774</v>
+        <v>1.014024972915649</v>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>-40.56679905371724</v>
+        <v>-40.08815292466483</v>
       </c>
       <c r="H10" t="n">
-        <v>-28.76102791145637</v>
+        <v>-29.57815563687181</v>
       </c>
       <c r="I10" t="n">
-        <v>-40.56679905371724</v>
+        <v>-40.08815292466483</v>
       </c>
       <c r="J10" t="n">
-        <v>-28.76102791145637</v>
+        <v>-29.57815563687181</v>
       </c>
       <c r="K10" t="n">
-        <v>5.458213085014512</v>
+        <v>9.103903606831187</v>
       </c>
       <c r="L10" t="n">
-        <v>53.90046135230829</v>
+        <v>52.59073030674698</v>
       </c>
     </row>
     <row r="11">
@@ -876,7 +876,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1566058778762817</v>
+        <v>0.8671839237213135</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
@@ -885,19 +885,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H11" t="n">
-        <v>-20.68144715421032</v>
+        <v>-14.00121697972564</v>
       </c>
       <c r="I11" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.68144715421032</v>
+        <v>-14.00121697972564</v>
       </c>
       <c r="K11" t="n">
-        <v>4.769390001619295</v>
+        <v>13.23784573467857</v>
       </c>
       <c r="L11" t="n">
-        <v>4.447604816439272</v>
+        <v>35.31159556089545</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01958387851715088</v>
+        <v>0.635502020517985</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -956,28 +956,30 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2325899839401245</v>
+        <v>8.413657903671265</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.64409077813305</v>
+        <v>9.33936568172531</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.966278081860844</v>
+        <v>9.33936568172531</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.64409077813305</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-8.966278081860844</v>
+        <v>9.33936568172531</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="K13" t="n">
-        <v>13.99450183655881</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>58.57401369375403</v>
+        <v>143.1497251488191</v>
       </c>
     </row>
     <row r="14">
@@ -998,28 +1000,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6648346996307373</v>
+        <v>1.160619020462036</v>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>-75.35989590507279</v>
+        <v>-32.00689898491509</v>
       </c>
       <c r="H14" t="n">
-        <v>-39.08409233567998</v>
+        <v>-28.74824458626204</v>
       </c>
       <c r="I14" t="n">
-        <v>-75.35989590507279</v>
+        <v>-32.00689898491509</v>
       </c>
       <c r="J14" t="n">
-        <v>-39.08409233567998</v>
+        <v>-28.74824458626204</v>
       </c>
       <c r="K14" t="n">
-        <v>12.42687070387934</v>
+        <v>4.672115214720751</v>
       </c>
       <c r="L14" t="n">
-        <v>68.27037912640918</v>
+        <v>76.66132569565572</v>
       </c>
     </row>
     <row r="15">
@@ -1040,28 +1042,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3304558801651001</v>
+        <v>0.8316149711608887</v>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>-27.61548458123839</v>
+        <v>0.7811316276853892</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.403669056140316</v>
+        <v>0.7811316276853892</v>
       </c>
       <c r="I15" t="n">
-        <v>-27.61548458123839</v>
+        <v>0.7811316276853892</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.403669056140316</v>
+        <v>0.7811316276853892</v>
       </c>
       <c r="K15" t="n">
-        <v>11.39434011463275</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>91.29593743296709</v>
+        <v>102.8286001116058</v>
       </c>
     </row>
     <row r="16">
@@ -1082,28 +1084,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4712372589111328</v>
+        <v>1.089413642883301</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>-71.80719911595767</v>
+        <v>-23.78164203533534</v>
       </c>
       <c r="H16" t="n">
-        <v>-26.02657236477818</v>
+        <v>-16.39608075702044</v>
       </c>
       <c r="I16" t="n">
-        <v>-71.80719911595767</v>
+        <v>-23.78164203533534</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.02657236477818</v>
+        <v>-16.39608075702044</v>
       </c>
       <c r="K16" t="n">
-        <v>16.66376248651869</v>
+        <v>6.75730052773552</v>
       </c>
       <c r="L16" t="n">
-        <v>78.87085961518927</v>
+        <v>86.68917722932235</v>
       </c>
     </row>
     <row r="17">
@@ -1124,28 +1126,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2863969850540161</v>
+        <v>0.8303050200144449</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.10149450173126</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.391550323478133</v>
+        <v>-7.709113266003283</v>
       </c>
       <c r="I17" t="n">
-        <v>-15.10149450173126</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.391550323478133</v>
+        <v>-7.709113266003283</v>
       </c>
       <c r="K17" t="n">
-        <v>6.464409965323789</v>
+        <v>18.11408434890731</v>
       </c>
       <c r="L17" t="n">
-        <v>94.96097807234013</v>
+        <v>72.08409201249086</v>
       </c>
     </row>
     <row r="18">
@@ -1166,31 +1168,25 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03673400402069091</v>
+        <v>0.7387136618296305</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
-      </c>
-      <c r="G18" t="n">
-        <v>23.0831481424233</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.0831481424233</v>
-      </c>
-      <c r="I18" t="n">
-        <v>23.0831481424233</v>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>118.7395816394435</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1210,28 +1206,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4431163787841797</v>
+        <v>9.056840022404989</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>7.9510728912868</v>
+        <v>23.0831481424233</v>
       </c>
       <c r="H19" t="n">
-        <v>21.87258212233238</v>
+        <v>23.0831481424233</v>
       </c>
       <c r="I19" t="n">
-        <v>7.9510728912868</v>
+        <v>23.0831481424233</v>
       </c>
       <c r="J19" t="n">
-        <v>21.87258212233238</v>
+        <v>23.0831481424233</v>
       </c>
       <c r="K19" t="n">
-        <v>4.146907628716611</v>
+        <v>4.351167857633658e-15</v>
       </c>
       <c r="L19" t="n">
-        <v>179.2040496627473</v>
+        <v>183.5876990480395</v>
       </c>
     </row>
     <row r="20">
@@ -1252,28 +1248,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3183314657211304</v>
+        <v>1.079414049784343</v>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>-54.95794061191005</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="H20" t="n">
-        <v>-14.94176359816955</v>
+        <v>-12.67642767201246</v>
       </c>
       <c r="I20" t="n">
-        <v>-54.95794061191005</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.94176359816955</v>
+        <v>-12.67642767201246</v>
       </c>
       <c r="K20" t="n">
-        <v>13.51407519088717</v>
+        <v>9.164614762531487</v>
       </c>
       <c r="L20" t="n">
-        <v>92.74197690710646</v>
+        <v>93.84237314595633</v>
       </c>
     </row>
     <row r="21">
@@ -1294,28 +1290,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2331216239929199</v>
+        <v>1.071667989095052</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>-30.7953932892736</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.24319209225417</v>
+        <v>-12.67642767201246</v>
       </c>
       <c r="I21" t="n">
-        <v>-30.7953932892736</v>
+        <v>-23.258813272346</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.24319209225417</v>
+        <v>-12.67642767201246</v>
       </c>
       <c r="K21" t="n">
-        <v>6.953064179049838</v>
+        <v>9.164614762531487</v>
       </c>
       <c r="L21" t="n">
-        <v>84.65841842846615</v>
+        <v>81.01407770016442</v>
       </c>
     </row>
     <row r="22">
@@ -1336,28 +1332,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3435420227050781</v>
+        <v>1.157729307810466</v>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>-50.28897681984679</v>
+        <v>-17.78412015969892</v>
       </c>
       <c r="H22" t="n">
-        <v>-14.78101032120997</v>
+        <v>-10.85152996779676</v>
       </c>
       <c r="I22" t="n">
-        <v>-50.28897681984679</v>
+        <v>-17.78412015969892</v>
       </c>
       <c r="J22" t="n">
-        <v>-14.78101032120997</v>
+        <v>-10.85152996779676</v>
       </c>
       <c r="K22" t="n">
-        <v>10.93980281345485</v>
+        <v>6.003799220214103</v>
       </c>
       <c r="L22" t="n">
-        <v>92.82006347224085</v>
+        <v>94.72882470787158</v>
       </c>
     </row>
     <row r="23">
@@ -1378,28 +1374,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2698701620101929</v>
+        <v>1.016474723815918</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.45491248806763</v>
+        <v>-7.385234871845686</v>
       </c>
       <c r="H23" t="n">
-        <v>-10.79751035980553</v>
+        <v>-7.385234871845686</v>
       </c>
       <c r="I23" t="n">
-        <v>-37.45491248806763</v>
+        <v>-7.385234871845686</v>
       </c>
       <c r="J23" t="n">
-        <v>-10.79751035980553</v>
+        <v>-7.385234871845686</v>
       </c>
       <c r="K23" t="n">
-        <v>6.319494424678306</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>83.82819686846426</v>
+        <v>88.93887938535934</v>
       </c>
     </row>
     <row r="24">
@@ -1420,31 +1416,25 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06154125690460205</v>
+        <v>0.8165253003438314</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.201937946842596</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.201937946842596</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.201937946842596</v>
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>4.864753555590494e-16</v>
-      </c>
-      <c r="L24" t="n">
-        <v>101.5553545207369</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1464,28 +1454,30 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7373441219329834</v>
+        <v>10.01209362347921</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>-17.19124270677605</v>
+        <v>3.201937946842596</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.017307880957558</v>
+        <v>3.201937946842596</v>
       </c>
       <c r="I25" t="n">
-        <v>-17.19124270677605</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-1.017307880957558</v>
+        <v>3.201937946842596</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="K25" t="n">
-        <v>5.612246373834981</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>98.47634295066314</v>
+        <v>104.7956527375506</v>
       </c>
     </row>
     <row r="26">
@@ -1506,7 +1498,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1014697551727295</v>
+        <v>0.258496363957723</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
@@ -1524,7 +1516,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K26" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1548,7 +1540,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07296319961547852</v>
+        <v>0.2187119325002035</v>
       </c>
       <c r="F27" t="n">
         <v>100</v>
@@ -1566,7 +1558,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K27" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1590,7 +1582,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06036032199859619</v>
+        <v>0.2048890590667725</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -1608,7 +1600,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K28" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1632,7 +1624,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04112500190734864</v>
+        <v>0.1918839613596598</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
@@ -1650,7 +1642,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K29" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1674,7 +1666,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002999005317687988</v>
+        <v>0.7427940368652344</v>
       </c>
       <c r="F30" t="n">
         <v>100</v>
@@ -1683,19 +1675,19 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="H30" t="n">
-        <v>-9.655609036796061</v>
+        <v>2.185310828724868</v>
       </c>
       <c r="I30" t="n">
         <v>-9.655609036796061</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.655609036796061</v>
+        <v>2.185310828724868</v>
       </c>
       <c r="K30" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>10.30004741000583</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>122.6325529585651</v>
       </c>
     </row>
     <row r="31">
@@ -1716,7 +1708,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03423496246337891</v>
+        <v>7.085788647333781</v>
       </c>
       <c r="F31" t="n">
         <v>100</v>
@@ -1734,7 +1726,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K31" t="n">
-        <v>1.794391381352886e-15</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1758,28 +1750,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E32" t="n">
-        <v>0.858689637184143</v>
+        <v>2.267364263534546</v>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>-83.17558374340292</v>
+        <v>-73.82195038041522</v>
       </c>
       <c r="H32" t="n">
-        <v>-40.87957988141083</v>
+        <v>-60.1243071816862</v>
       </c>
       <c r="I32" t="n">
-        <v>-83.17558374340292</v>
+        <v>-73.82195038041522</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.87957988141083</v>
+        <v>-60.1243071816862</v>
       </c>
       <c r="K32" t="n">
-        <v>15.72166587720408</v>
+        <v>14.01334894732757</v>
       </c>
       <c r="L32" t="n">
-        <v>86.67124933850226</v>
+        <v>80.39652311876118</v>
       </c>
     </row>
     <row r="33">
@@ -1800,28 +1792,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7015517997741699</v>
+        <v>1.714800596237183</v>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>-73.82012908285937</v>
+        <v>-26.43926212615339</v>
       </c>
       <c r="H33" t="n">
-        <v>-33.40258291847693</v>
+        <v>-15.72144663969139</v>
       </c>
       <c r="I33" t="n">
-        <v>-73.82012908285937</v>
+        <v>-26.43926212615339</v>
       </c>
       <c r="J33" t="n">
-        <v>-33.40258291847693</v>
+        <v>-15.72144663969139</v>
       </c>
       <c r="K33" t="n">
-        <v>14.52523431881931</v>
+        <v>10.84939684728863</v>
       </c>
       <c r="L33" t="n">
-        <v>68.31791275361125</v>
+        <v>85.08833148341274</v>
       </c>
     </row>
     <row r="34">
@@ -1842,28 +1834,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6787927627563477</v>
+        <v>1.905480305353801</v>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>-67.34428852594259</v>
+        <v>-55.92687009972038</v>
       </c>
       <c r="H34" t="n">
-        <v>-29.93657616265235</v>
+        <v>-45.83758718621809</v>
       </c>
       <c r="I34" t="n">
-        <v>-67.34428852594259</v>
+        <v>-55.92687009972038</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.93657616265235</v>
+        <v>-45.83758718621809</v>
       </c>
       <c r="K34" t="n">
-        <v>12.96543610986399</v>
+        <v>8.775454488839715</v>
       </c>
       <c r="L34" t="n">
-        <v>90.23920596815198</v>
+        <v>85.05469546648679</v>
       </c>
     </row>
     <row r="35">
@@ -1884,28 +1876,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5811501741409302</v>
+        <v>1.694896697998047</v>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>-48.70961047200002</v>
+        <v>-30.89595283632912</v>
       </c>
       <c r="H35" t="n">
-        <v>-26.55325452426786</v>
+        <v>-22.83044460112324</v>
       </c>
       <c r="I35" t="n">
-        <v>-48.70961047200002</v>
+        <v>-30.89595283632912</v>
       </c>
       <c r="J35" t="n">
-        <v>-26.55325452426786</v>
+        <v>-22.83044460112324</v>
       </c>
       <c r="K35" t="n">
-        <v>10.15771262887356</v>
+        <v>9.408167387855213</v>
       </c>
       <c r="L35" t="n">
-        <v>74.81444687775718</v>
+        <v>78.34550281659438</v>
       </c>
     </row>
     <row r="36">
@@ -1926,7 +1918,7 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09215949535369873</v>
+        <v>0.9655413627624512</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1964,31 +1956,25 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E37" t="n">
-        <v>1.089952220916748</v>
+        <v>11.07987395922343</v>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-7.544969236804366</v>
-      </c>
-      <c r="H37" t="n">
-        <v>12.52536774204873</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-7.544969236804366</v>
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>16.72522542298737</v>
-      </c>
-      <c r="L37" t="n">
-        <v>111.8802128136379</v>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/graphs_non_dag/benchmark_results.xlsx
+++ b/results/graphs_non_dag/benchmark_results.xlsx
@@ -496,7 +496,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5500526428222656</v>
+        <v>0.2555058002471924</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -505,19 +505,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.9375682122237</v>
+        <v>-17.32019793967429</v>
       </c>
       <c r="I2" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J2" t="n">
-        <v>-15.9375682122237</v>
+        <v>-17.32019793967429</v>
       </c>
       <c r="K2" t="n">
-        <v>5.401263533451655</v>
+        <v>4.193073306928126</v>
       </c>
       <c r="L2" t="n">
-        <v>28.12630358880562</v>
+        <v>21.89105439917971</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4201946258544922</v>
+        <v>0.1407076644897461</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -556,7 +556,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8.97195690676443e-16</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.506061315536499</v>
+        <v>0.1866178035736084</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -589,19 +589,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="H4" t="n">
-        <v>-19.3457020010964</v>
+        <v>-16.89009622837542</v>
       </c>
       <c r="I4" t="n">
         <v>-22.17441012222855</v>
       </c>
       <c r="J4" t="n">
-        <v>-19.3457020010964</v>
+        <v>-16.89009622837542</v>
       </c>
       <c r="K4" t="n">
-        <v>3.268361972261306</v>
+        <v>3.445170494420302</v>
       </c>
       <c r="L4" t="n">
-        <v>12.75663300867941</v>
+        <v>23.83068530222554</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3809603055318196</v>
+        <v>0.09856816291809083</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -640,7 +640,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.97195690676443e-16</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -664,19 +664,19 @@
         <v>-22.17441012222855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6743262608846029</v>
+        <v>0.5660290002822876</v>
       </c>
       <c r="F6" t="n">
-        <v>33.33333333333333</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>18.48045501250461</v>
+        <v>-12.66100222106747</v>
       </c>
       <c r="H6" t="n">
-        <v>18.48045501250461</v>
+        <v>2.482525680343125</v>
       </c>
       <c r="I6" t="n">
-        <v>18.48045501250461</v>
+        <v>-12.66100222106747</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>26.22935973108004</v>
       </c>
       <c r="L6" t="n">
-        <v>183.3413602014109</v>
+        <v>111.1954530770338</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +708,7 @@
         <v>5.779070637709793</v>
       </c>
       <c r="E7" t="n">
-        <v>7.364137411117554</v>
+        <v>6.781086978912353</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -717,19 +717,19 @@
         <v>5.779070637709793</v>
       </c>
       <c r="H7" t="n">
-        <v>5.779070637709793</v>
+        <v>7.179333466728301</v>
       </c>
       <c r="I7" t="n">
         <v>5.779070637709793</v>
       </c>
       <c r="J7" t="n">
-        <v>5.779070637709793</v>
+        <v>7.179333466728301</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.429727019635979</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>24.22989641070424</v>
       </c>
     </row>
     <row r="8">
@@ -750,28 +750,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E8" t="n">
-        <v>1.04619296391805</v>
+        <v>0.3495679187774658</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>-37.51101427360693</v>
+        <v>-45.22413787382439</v>
       </c>
       <c r="H8" t="n">
-        <v>-32.22203977511564</v>
+        <v>-32.57906711485907</v>
       </c>
       <c r="I8" t="n">
-        <v>-37.51101427360693</v>
+        <v>-45.22413787382439</v>
       </c>
       <c r="J8" t="n">
-        <v>-32.22203977511564</v>
+        <v>-32.57906711485907</v>
       </c>
       <c r="K8" t="n">
-        <v>9.160772551323042</v>
+        <v>6.274897640157038</v>
       </c>
       <c r="L8" t="n">
-        <v>48.35298750470891</v>
+        <v>47.78072716347719</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9062723318735758</v>
+        <v>0.1980668210983276</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -810,10 +810,10 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.588782762705772e-15</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.641424310782227e-14</v>
       </c>
     </row>
     <row r="10">
@@ -834,28 +834,28 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E10" t="n">
-        <v>1.014024972915649</v>
+        <v>0.2487722826004028</v>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>-40.08815292466483</v>
+        <v>-42.51757193310117</v>
       </c>
       <c r="H10" t="n">
-        <v>-29.57815563687181</v>
+        <v>-28.73056861845623</v>
       </c>
       <c r="I10" t="n">
-        <v>-40.08815292466483</v>
+        <v>-42.51757193310117</v>
       </c>
       <c r="J10" t="n">
-        <v>-29.57815563687181</v>
+        <v>-28.73056861845623</v>
       </c>
       <c r="K10" t="n">
-        <v>9.103903606831187</v>
+        <v>6.029657254063</v>
       </c>
       <c r="L10" t="n">
-        <v>52.59073030674698</v>
+        <v>53.94928295072834</v>
       </c>
     </row>
     <row r="11">
@@ -876,7 +876,7 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8671839237213135</v>
+        <v>0.1561547994613647</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
@@ -885,19 +885,19 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.00121697972564</v>
+        <v>-20.66283797573633</v>
       </c>
       <c r="I11" t="n">
         <v>-21.64409077813305</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.00121697972564</v>
+        <v>-20.66283797573633</v>
       </c>
       <c r="K11" t="n">
-        <v>13.23784573467857</v>
+        <v>4.862011615635376</v>
       </c>
       <c r="L11" t="n">
-        <v>35.31159556089545</v>
+        <v>4.533582918567657</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>-62.38897124602023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.635502020517985</v>
+        <v>0.6170758152008057</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -956,16 +956,16 @@
         <v>-21.64409077813305</v>
       </c>
       <c r="E13" t="n">
-        <v>8.413657903671265</v>
+        <v>11.77217942237854</v>
       </c>
       <c r="F13" t="n">
-        <v>66.66666666666666</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
         <v>9.33936568172531</v>
       </c>
       <c r="H13" t="n">
-        <v>9.33936568172531</v>
+        <v>17.50386643830041</v>
       </c>
       <c r="I13" t="n">
         <v>9.33936568172531</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14.72774207827816</v>
       </c>
       <c r="L13" t="n">
-        <v>143.1497251488191</v>
+        <v>180.8713409018987</v>
       </c>
     </row>
     <row r="14">
@@ -1000,28 +1000,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E14" t="n">
-        <v>1.160619020462036</v>
+        <v>0.5988937759399414</v>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>-32.00689898491509</v>
+        <v>-64.57307597239539</v>
       </c>
       <c r="H14" t="n">
-        <v>-28.74824458626204</v>
+        <v>-32.22692144511327</v>
       </c>
       <c r="I14" t="n">
-        <v>-32.00689898491509</v>
+        <v>-64.57307597239539</v>
       </c>
       <c r="J14" t="n">
-        <v>-28.74824458626204</v>
+        <v>-32.22692144511327</v>
       </c>
       <c r="K14" t="n">
-        <v>4.672115214720751</v>
+        <v>14.02122788582326</v>
       </c>
       <c r="L14" t="n">
-        <v>76.66132569565572</v>
+        <v>73.83723304627058</v>
       </c>
     </row>
     <row r="15">
@@ -1042,28 +1042,28 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8316149711608887</v>
+        <v>0.3214789390563965</v>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7811316276853892</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7811316276853892</v>
+        <v>-4.728643934405106</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7811316276853892</v>
+        <v>-27.61548458123839</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7811316276853892</v>
+        <v>-4.728643934405106</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10.37791392766633</v>
       </c>
       <c r="L15" t="n">
-        <v>102.8286001116058</v>
+        <v>82.87683882390503</v>
       </c>
     </row>
     <row r="16">
@@ -1084,28 +1084,28 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E16" t="n">
-        <v>1.089413642883301</v>
+        <v>0.4861707019805908</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>-23.78164203533534</v>
+        <v>-64.34817848610757</v>
       </c>
       <c r="H16" t="n">
-        <v>-16.39608075702044</v>
+        <v>-22.55524476135864</v>
       </c>
       <c r="I16" t="n">
-        <v>-23.78164203533534</v>
+        <v>-64.34817848610757</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.39608075702044</v>
+        <v>-22.55524476135864</v>
       </c>
       <c r="K16" t="n">
-        <v>6.75730052773552</v>
+        <v>12.84005030465254</v>
       </c>
       <c r="L16" t="n">
-        <v>86.68917722932235</v>
+        <v>81.68898592188572</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8303050200144449</v>
+        <v>0.2895294380187988</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
@@ -1135,19 +1135,19 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.709113266003283</v>
+        <v>-1.387952426716674</v>
       </c>
       <c r="I17" t="n">
         <v>-27.61548458123839</v>
       </c>
       <c r="J17" t="n">
-        <v>-7.709113266003283</v>
+        <v>-1.387952426716674</v>
       </c>
       <c r="K17" t="n">
-        <v>18.11408434890731</v>
+        <v>9.432574063228836</v>
       </c>
       <c r="L17" t="n">
-        <v>72.08409201249086</v>
+        <v>94.97400662069269</v>
       </c>
     </row>
     <row r="18">
@@ -1168,25 +1168,31 @@
         <v>-123.1785670915798</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7387136618296305</v>
+        <v>0.6949715185165405</v>
       </c>
       <c r="F18" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>23.0831481424233</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.0831481424233</v>
+      </c>
+      <c r="I18" t="n">
+        <v>23.0831481424233</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>118.7395816394435</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1206,7 +1212,7 @@
         <v>-27.61548458123839</v>
       </c>
       <c r="E19" t="n">
-        <v>9.056840022404989</v>
+        <v>8.507108960151673</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
@@ -1224,7 +1230,7 @@
         <v>23.0831481424233</v>
       </c>
       <c r="K19" t="n">
-        <v>4.351167857633658e-15</v>
+        <v>7.177565525411544e-15</v>
       </c>
       <c r="L19" t="n">
         <v>183.5876990480395</v>
@@ -1248,28 +1254,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E20" t="n">
-        <v>1.079414049784343</v>
+        <v>0.3300312185287476</v>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.258813272346</v>
+        <v>-60.84865582626207</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.67642767201246</v>
+        <v>-14.45011191416253</v>
       </c>
       <c r="I20" t="n">
-        <v>-23.258813272346</v>
+        <v>-60.84865582626207</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.67642767201246</v>
+        <v>-14.45011191416253</v>
       </c>
       <c r="K20" t="n">
-        <v>9.164614762531487</v>
+        <v>12.99684120201363</v>
       </c>
       <c r="L20" t="n">
-        <v>93.84237314595633</v>
+        <v>92.98079873377625</v>
       </c>
     </row>
     <row r="21">
@@ -1290,28 +1296,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E21" t="n">
-        <v>1.071667989095052</v>
+        <v>0.220543098449707</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>-23.258813272346</v>
+        <v>-37.82420185221456</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.67642767201246</v>
+        <v>-9.715115941719766</v>
       </c>
       <c r="I21" t="n">
-        <v>-23.258813272346</v>
+        <v>-37.82420185221456</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.67642767201246</v>
+        <v>-9.715115941719766</v>
       </c>
       <c r="K21" t="n">
-        <v>9.164614762531487</v>
+        <v>5.965849729882696</v>
       </c>
       <c r="L21" t="n">
-        <v>81.01407770016442</v>
+        <v>85.44933626603473</v>
       </c>
     </row>
     <row r="22">
@@ -1332,28 +1338,28 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E22" t="n">
-        <v>1.157729307810466</v>
+        <v>0.3035334539413452</v>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.78412015969892</v>
+        <v>-51.82416035848922</v>
       </c>
       <c r="H22" t="n">
-        <v>-10.85152996779676</v>
+        <v>-12.26486078069614</v>
       </c>
       <c r="I22" t="n">
-        <v>-17.78412015969892</v>
+        <v>-51.82416035848922</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.85152996779676</v>
+        <v>-12.26486078069614</v>
       </c>
       <c r="K22" t="n">
-        <v>6.003799220214103</v>
+        <v>10.22573099148742</v>
       </c>
       <c r="L22" t="n">
-        <v>94.72882470787158</v>
+        <v>94.04229345535073</v>
       </c>
     </row>
     <row r="23">
@@ -1374,28 +1380,28 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E23" t="n">
-        <v>1.016474723815918</v>
+        <v>0.2730586385726929</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.385234871845686</v>
+        <v>-25.2631210895704</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.385234871845686</v>
+        <v>-8.933921597289903</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.385234871845686</v>
+        <v>-25.2631210895704</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.385234871845686</v>
+        <v>-8.933921597289903</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3.610996179870355</v>
       </c>
       <c r="L23" t="n">
-        <v>88.93887938535934</v>
+        <v>86.61935793997702</v>
       </c>
     </row>
     <row r="24">
@@ -1416,25 +1422,31 @@
         <v>-205.8654733793739</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8165253003438314</v>
+        <v>0.7898713731765747</v>
       </c>
       <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.201937946842596</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>101.5553545207369</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1454,10 +1466,10 @@
         <v>-66.767510536595</v>
       </c>
       <c r="E25" t="n">
-        <v>10.01209362347921</v>
+        <v>9.679683380126953</v>
       </c>
       <c r="F25" t="n">
-        <v>33.33333333333333</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
         <v>3.201937946842596</v>
@@ -1498,7 +1510,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.258496363957723</v>
+        <v>0.1020892190933227</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
@@ -1516,7 +1528,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1540,7 +1552,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2187119325002035</v>
+        <v>0.07380496025085449</v>
       </c>
       <c r="F27" t="n">
         <v>100</v>
@@ -1558,7 +1570,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1582,7 +1594,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2048890590667725</v>
+        <v>0.05946427822113037</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -1600,7 +1612,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1624,7 +1636,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1918839613596598</v>
+        <v>0.03979621887207031</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
@@ -1642,7 +1654,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1666,7 +1678,7 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7427940368652344</v>
+        <v>0.5431041765213013</v>
       </c>
       <c r="F30" t="n">
         <v>100</v>
@@ -1675,19 +1687,19 @@
         <v>-9.655609036796061</v>
       </c>
       <c r="H30" t="n">
-        <v>2.185310828724868</v>
+        <v>-0.5234520621522794</v>
       </c>
       <c r="I30" t="n">
         <v>-9.655609036796061</v>
       </c>
       <c r="J30" t="n">
-        <v>2.185310828724868</v>
+        <v>-0.5234520621522794</v>
       </c>
       <c r="K30" t="n">
-        <v>10.30004741000583</v>
+        <v>9.243725904769788</v>
       </c>
       <c r="L30" t="n">
-        <v>122.6325529585651</v>
+        <v>94.57877737015363</v>
       </c>
     </row>
     <row r="31">
@@ -1708,7 +1720,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="E31" t="n">
-        <v>7.085788647333781</v>
+        <v>6.545995998382568</v>
       </c>
       <c r="F31" t="n">
         <v>100</v>
@@ -1726,7 +1738,7 @@
         <v>9.072951821112582</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.794391381352886e-15</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1750,28 +1762,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E32" t="n">
-        <v>2.267364263534546</v>
+        <v>0.9072353172302247</v>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>-73.82195038041522</v>
+        <v>-71.76747431216</v>
       </c>
       <c r="H32" t="n">
-        <v>-60.1243071816862</v>
+        <v>-45.28766830212454</v>
       </c>
       <c r="I32" t="n">
-        <v>-73.82195038041522</v>
+        <v>-71.76747431216</v>
       </c>
       <c r="J32" t="n">
-        <v>-60.1243071816862</v>
+        <v>-45.28766830212454</v>
       </c>
       <c r="K32" t="n">
-        <v>14.01334894732757</v>
+        <v>15.38998727565907</v>
       </c>
       <c r="L32" t="n">
-        <v>80.39652311876118</v>
+        <v>85.23399602954042</v>
       </c>
     </row>
     <row r="33">
@@ -1792,28 +1804,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E33" t="n">
-        <v>1.714800596237183</v>
+        <v>0.6911885023117066</v>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>-26.43926212615339</v>
+        <v>-65.06219690028034</v>
       </c>
       <c r="H33" t="n">
-        <v>-15.72144663969139</v>
+        <v>-31.54581074594377</v>
       </c>
       <c r="I33" t="n">
-        <v>-26.43926212615339</v>
+        <v>-65.06219690028034</v>
       </c>
       <c r="J33" t="n">
-        <v>-15.72144663969139</v>
+        <v>-31.54581074594377</v>
       </c>
       <c r="K33" t="n">
-        <v>10.84939684728863</v>
+        <v>13.64170191199423</v>
       </c>
       <c r="L33" t="n">
-        <v>85.08833148341274</v>
+        <v>70.07904655905483</v>
       </c>
     </row>
     <row r="34">
@@ -1834,28 +1846,28 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E34" t="n">
-        <v>1.905480305353801</v>
+        <v>0.7480438423156738</v>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>-55.92687009972038</v>
+        <v>-84.47338038585237</v>
       </c>
       <c r="H34" t="n">
-        <v>-45.83758718621809</v>
+        <v>-30.46578258208369</v>
       </c>
       <c r="I34" t="n">
-        <v>-55.92687009972038</v>
+        <v>-84.47338038585237</v>
       </c>
       <c r="J34" t="n">
-        <v>-45.83758718621809</v>
+        <v>-30.46578258208369</v>
       </c>
       <c r="K34" t="n">
-        <v>8.775454488839715</v>
+        <v>14.45031278015318</v>
       </c>
       <c r="L34" t="n">
-        <v>85.05469546648679</v>
+        <v>90.06665868577953</v>
       </c>
     </row>
     <row r="35">
@@ -1876,28 +1888,28 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E35" t="n">
-        <v>1.694896697998047</v>
+        <v>0.6173372030258178</v>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>-30.89595283632912</v>
+        <v>-58.98209937305561</v>
       </c>
       <c r="H35" t="n">
-        <v>-22.83044460112324</v>
+        <v>-25.95012760841225</v>
       </c>
       <c r="I35" t="n">
-        <v>-30.89595283632912</v>
+        <v>-58.98209937305561</v>
       </c>
       <c r="J35" t="n">
-        <v>-22.83044460112324</v>
+        <v>-25.95012760841225</v>
       </c>
       <c r="K35" t="n">
-        <v>9.408167387855213</v>
+        <v>10.89032332389667</v>
       </c>
       <c r="L35" t="n">
-        <v>78.34550281659438</v>
+        <v>75.3865080149279</v>
       </c>
     </row>
     <row r="36">
@@ -1918,7 +1930,7 @@
         <v>-306.7022627972041</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9655413627624512</v>
+        <v>0.9014909601211548</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1956,7 +1968,7 @@
         <v>-105.430499760663</v>
       </c>
       <c r="E37" t="n">
-        <v>11.07987395922343</v>
+        <v>11.2375063753128</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
